--- a/balance_generate/input_data/interest_rt.xlsx
+++ b/balance_generate/input_data/interest_rt.xlsx
@@ -423,12 +423,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>margin_pct</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -465,9 +465,6 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -630,11 +627,14 @@
       <c r="B14" t="n">
         <v>0.1</v>
       </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="15">
